--- a/PO_TBD_20260528.xlsx
+++ b/PO_TBD_20260528.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>CAP TRACIDOL (TRAMADOL) 50MG Y.S.P.</t>
+          <t>TAB TREN (TRANEXAMIC ACID) 250MG</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -633,13 +633,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="11">
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>TAB UNASYN (SULTAMICILLIN) 375MG PFIZER</t>
+          <t>CAP TRACIDOL (TRAMADOL) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>281.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -680,7 +680,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TAB PREDNISYN (PREDNISOLONE) 5MG DUOPHARMA</t>
+          <t>TAB UNASYN (SULTAMICILLIN) 375MG PFIZER</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -697,13 +697,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.074</v>
+        <v>4.2</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>5.33</v>
+        <v>289.8</v>
       </c>
     </row>
     <row r="13">
@@ -712,7 +712,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>TAB PARACAP 500MG HEALTH PHARM</t>
+          <t>TAB CRESTOR ( ROSUVASTATIN ) 20MG ASTRAZENECA</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.157</v>
+        <v>6.24286</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>27</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -744,7 +744,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
+          <t>TAB PREDNISYN (PREDNISOLONE) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.5</v>
+        <v>0.074</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>6</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
+          <t>SUSP CURAM (AMOXYCILLIN + CLAVULANIC ACID) 312.5MG/5ML 60ML SANDOZ</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -786,20 +786,20 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.119</v>
+        <v>10.91</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>1.43</v>
+        <v>32.73</v>
       </c>
     </row>
     <row r="16">
@@ -808,7 +808,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
+          <t>SYR NUROFEN (IBUPROFEN) 100MG/5ML 60ML RB HEALTH</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.203</v>
+        <v>6.46</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3.45</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
+          <t>SYR CHLORAMINE (CHLORPHENIRAMINE) 2.5MG/5ML 90ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -850,20 +850,20 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SUSP CURAM (AMOXYCILLIN + CLAVULANIC ACID) 312.5MG/5ML 60ML SANDOZ</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 12.5MG Y.SP.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -882,20 +882,20 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>10.91</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>10.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -904,7 +904,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>TAB PONTALON (MEFENAMIC ACID) 500MG Y.S.P.</t>
+          <t>PRISTINE SHAMPOO (KETOCONAZOLE 2%) 20MG 120ML XEPA</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -914,20 +914,20 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.143</v>
+        <v>17.2</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>1.72</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="20">
@@ -936,7 +936,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
+          <t>SYR MUCOPROM (CARBOCISTEINE 100MG/ PROMETHAZINE 2.5MG /5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -946,20 +946,20 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1.75</v>
+        <v>7.2</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>17.5</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="21">
@@ -968,7 +968,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
+          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>RESPULE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>4.82</v>
+        <v>7.9</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9.640000000000001</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="22">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
+          <t>MAC DUAL (HEXYLRESORCINOL 2.4MG) ACTION LOZENGES ZIWELL</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>LOZENGES</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>42.4</v>
+        <v>1.06667</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>42.4</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="23">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
+          <t>TAB ESOZ (ESOMEPRAZOLE) 40MG RANBAXY</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1042,20 +1042,20 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>1.66</v>
+        <v>1.783</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>3.32</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="24">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
+          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1074,20 +1074,20 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>4.91</v>
+        <v>11.36</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>9.82</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="25">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
+          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1106,20 +1106,20 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1138,20 +1138,20 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.459</v>
+        <v>118</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>12.85</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+          <t>IVD SODIUM LACTATE (HARTMANN SOLUTION) 500ML AIN MEDICARE</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1170,20 +1170,20 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1202,20 +1202,20 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.065</v>
+        <v>3.4</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.78</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="29">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
+          <t>TAB APROVASC ( IRBESARTAN150MG / AMLODIPINE 5MG) SANOFI</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.164</v>
+        <v>1.40107</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>16.4</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="30">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>INFUSOL N/S 500ML ( SODIUM CHLORIDE 0.9% W/V ) AIN MEDICARE</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1266,20 +1266,20 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0.584</v>
+        <v>4.5</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>3.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1298,20 +1298,20 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="32">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
+          <t>ORS PLUS (TRISODIUM CITRATE 725MG, DEXTROSE ANHYDROUS 3375MG, SODIUM CHLORIDE 650MG, POTASSIUM CHLORIDE 375MG) SACHET PHARMANIAGA</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>26.1</v>
+        <v>0.39</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>26.1</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="33">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+          <t>LOZENGES DIFFLAM (BENZYDAMINE HYDROCHLORIDE 3MG) MINT FLAVOURED INOVA</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1362,20 +1362,20 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>LOZENGES</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>8.15</v>
+        <v>1.62333</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.15</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
+          <t>TAB PROBITOR ( OMEPRAZOLE ) 20MG SANDOZ</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>3.675</v>
+        <v>0.53571</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>25.72</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="35">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
+          <t>CREAM LAMISIL (TERBINAFINE HYDROCHLORIDE) 10MG/G 15G ZUELLIG</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1426,20 +1426,20 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>SYR MUCOPROM (CARBOCISTEINE 100MG/ PROMETHAZINE 2.5MG /5ML) 90ML XEPA</t>
+          <t>ZYNOMAX ( AZITHROMYCIN ) POWDER FOR ORAL SUSPENSION 200MG/5ML 20ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1465,13 +1465,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>14.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
+          <t>WELLMEX ATOMIC ENEMA 20ML NGL TRADING</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1490,20 +1490,20 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.24</v>
+        <v>2.678</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>4.08</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="38">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
+          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>16.56</v>
+        <v>5.06667</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>33.12</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>SYR CEFUROXIME-125 (125MG/5ML) 50ML AXCEL KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AXCEL</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>32</v>
+        <v>21.2</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>96</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="40">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+          <t>TABLET COZAAR XQ 5/50MG ORGANON</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1586,20 +1586,20 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>5</v>
+        <v>2.69667</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>20</v>
+        <v>126.74</v>
       </c>
     </row>
     <row r="41">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1618,20 +1618,20 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>12.5</v>
+        <v>103.66667</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>25</v>
+        <v>2591.67</v>
       </c>
     </row>
     <row r="42">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>5.5</v>
+        <v>97</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
+          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -1682,20 +1682,20 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>9</v>
+        <v>0.527</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>18</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="44">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>7.9</v>
+        <v>106.5</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>23.7</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="45">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>NASONEX AQUEOUS NASAL SPRAY 0.05% 60D (MOMETASONE FUROATE) SCENT-FREE ORGANON HEIST BV</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1746,20 +1746,20 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>1.617</v>
+        <v>0</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>19.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>MAC DUAL (HEXYLRESORCINOL 2.4MG) ACTION LOZENGES ZIWELL</t>
+          <t>TAB ROSUVASTATIN 20MG SYNERRV</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1778,20 +1778,20 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>LOZENGES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1.06667</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>10.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
+          <t>TAB ATORVASTATIN 20MG SYNERRV</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TAB ESOZ (ESOMEPRAZOLE) 40MG RANBAXY</t>
+          <t>TAB ZIOMYCIN (AZITHROMYCIN) 500MG SYNERRV</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1849,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1.783</v>
+        <v>0</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB ZIOMYCIN (AZITHROMYCIN) 250MG SYNERRV</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1874,20 +1874,20 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
+          <t>TAB GLIT (PIOGLITAZONE) 30MG SYNERRV</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>11.36</v>
+        <v>0</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>11.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
+          <t>TAB GLIT (PIOGLITAZONE) 15MG SYNERRV</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1938,14 +1938,14 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
+          <t>DYNA CALAMINE LOTION (CALAMINE POWDER 15% W/V / MENTHOL 0.15% W/V) 100ML DYNAPHARM (M)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1970,20 +1970,20 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>1.814</v>
+        <v>6.36667</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>150.56</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
+          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2002,20 +2002,20 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>236</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
+          <t>INJ TROVITE PAIR (THIAMINE HYDROCHLORIDE 250MG/5ML + PYRIDOXINE HYDROCHLORIDE 50MG/5ML + DEXTROSE MONOHYDRATE 1000MG/5ML + ASCORBIC ACID 500MG/5ML + DEXPANTHENOL 5MG/5ML + RIBOFLAVIN SODIUM PHOSPHATE 5.133MG/5ML + NICOTINAMIDE 160MG/5ML) DUOPHARMA</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2034,20 +2034,20 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>AMPULE PAIR</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>3.4</v>
+        <v>35.4</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>20.4</v>
+        <v>212.4</v>
       </c>
     </row>
     <row r="55">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
+          <t>TAB PARACAP 500MG HEALTH PHARM</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2066,20 +2066,20 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>440</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>13.64</v>
+        <v>0.157</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>13.64</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="56">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0.73</v>
+        <v>0.459</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>4.38</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="57">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>TAB SPASIL (DIPHENOXYLATE 2.5MG/ATROPINE 0.025MG) IMEKS</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2134,16 +2134,16 @@
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>6</v>
+        <v>205</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>1.06</v>
+        <v>0.164</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.36</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>INJ TROVITE PAIR (THIAMINE HYDROCHLORIDE 250MG/5ML + PYRIDOXINE HYDROCHLORIDE 50MG/5ML + DEXTROSE MONOHYDRATE 1000MG/5ML + ASCORBIC ACID 500MG/5ML + DEXPANTHENOL 5MG/5ML + RIBOFLAVIN SODIUM PHOSPHATE 5.133MG/5ML + NICOTINAMIDE 160MG/5ML) DUOPHARMA</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2162,20 +2162,20 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AMPULE PAIR</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>35.4</v>
+        <v>1.814</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>106.2</v>
+        <v>308.38</v>
       </c>
     </row>
     <row r="59">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2194,20 +2194,20 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>3.48</v>
+        <v>0.089</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.96</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.232</v>
+        <v>0.5</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>1.39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
+          <t>TAB VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -2258,20 +2258,20 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>15</v>
+        <v>0.119</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>30</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
+          <t>TAB IBUPROFEN 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2290,20 +2290,20 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>9.5</v>
+        <v>0.203</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>19</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>CANDACORT CREAM (CLOTRIMAZOLE 1% / HYDROCORTISONE 1% ) 15G HOE</t>
+          <t>TAB PONTALON (MEFENAMIC ACID) 500MG Y.S.P.</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>8.15</v>
+        <v>0.143</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.15</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+          <t>INJ PIRIMAT (CHLORPHENIRAMINE) 10MG/ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2354,20 +2354,20 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>7.7</v>
+        <v>1.75</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>7.7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>ORS PLUS (TRISODIUM CITRATE 725MG, DEXTROSE ANHYDROUS 3375MG, SODIUM CHLORIDE 650MG, POTASSIUM CHLORIDE 375MG) SACHET PHARMANIAGA</t>
+          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2386,20 +2386,20 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>5.07</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="66">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>LOZENGES DIFFLAM (BENZYDAMINE HYDROCHLORIDE 3MG) MINT FLAVOURED INOVA</t>
+          <t>TAB DUOFOLIC (FOLIC ACID) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2418,20 +2418,20 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>LOZENGES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>27</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>1.62333</v>
+        <v>0.065</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>43.83</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="67">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>AEVA THYMOL GARGLE 120ML APEX</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2450,20 +2450,20 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>5.3</v>
+        <v>0.584</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>5.3</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="68">
@@ -2472,30 +2472,30 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+          <t>CAP LOMODIUM (LOPERAMIDE) 2MG DYNAPHARM</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>DRIMINATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>1.29</v>
+        <v>0.093</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2514,20 +2514,20 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>ZYNOMAX ( AZITHROMYCIN ) POWDER FOR ORAL SUSPENSION 200MG/5ML 20ML DUOPHARMA</t>
+          <t>TAB DUPHASTON (DYDROGESTERONE) 10MG ABBOTT</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2546,20 +2546,20 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>12</v>
+        <v>3.675</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>12</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+          <t>TAB NEXIUM MUPS (ESOMEPRAZOLE) 40MG ASTRAZENECA</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>0.5ML</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>3.75</v>
+        <v>6.77857</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>15</v>
+        <v>284.7</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2610,20 +2610,20 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>WELLMEX ATOMIC ENEMA 20ML NGL TRADING</t>
+          <t>TAB HOVASC (AMLODIPINE) 5MG HOVID</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2642,20 +2642,20 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>2.678</v>
+        <v>0.24</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.029999999999999</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="74">
@@ -2664,30 +2664,30 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>SYR CEFUROXIME-125 (125MG/5ML) 50ML AXCEL KOTRA PHARMA</t>
+          <t>TAB HOVASC (AMLODIPINE) 10MG HOVID</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>AXCEL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>21.2</v>
+        <v>0.35</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>21.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="75">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
+          <t>TAB NORMATEN (ATENOLOL) 50MG XEPA</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -2706,20 +2706,20 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>BTL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>3.27</v>
+        <v>0.26786</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.54</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="76">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TABLET COZAAR XQ 5/50MG ORGANON</t>
+          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>2.69667</v>
+        <v>0.438</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>45.84</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="77">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -2770,20 +2770,20 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>103.66667</v>
+        <v>1.617</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>1451.33</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="78">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>TAB COPASTIN (CLOPERASTINE) 10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2809,13 +2809,13 @@
         <v>100</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.089</v>
+        <v>0.236</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>7.39</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="79">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2834,20 +2834,20 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>8.4</v>
+        <v>1.53</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>16.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="80">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2866,20 +2866,20 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="81">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>TAB ROSUVASTATIN 20MG SYNERRV</t>
+          <t>TAB CAFFOX ( ERGOTAMINE TARTRATE 1MG + CAFFINE 100MG ) IMEKS</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2902,16 +2902,16 @@
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>0</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="82">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TAB ATORVASTATIN 20MG SYNERRV</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="83">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 500MG SYNERRV</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="84">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 250MG SYNERRV</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>0</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="85">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 30MG SYNERRV</t>
+          <t>TAB DULCOLAX ( BISACODYL ) 5MG SANOFI</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="86">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 15MG SYNERRV</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>0</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="87">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -3090,20 +3090,20 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>30</v>
+        <v>1.44</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>60</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="88">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>DYNA CALAMINE LOTION (CALAMINE POWDER 15% W/V / MENTHOL 0.15% W/V) 100ML DYNAPHARM (M)</t>
+          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>6.36667</v>
+        <v>5.5</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>12.73</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="89">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+          <t>NEBULE VENTOLIN (SALBUTAMOL) 2.5MG/2.5ML GSK</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -3154,20 +3154,20 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>35.71429</v>
+        <v>4.82</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>71.43000000000001</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="90">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
+          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3186,20 +3186,20 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="91">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -3218,20 +3218,20 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>3</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="92">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 50MG Y.S.P.</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -3250,20 +3250,20 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>7.5</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="93">
@@ -3272,58 +3272,1594 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
+          <t>CAP BIOZOLE (FLUCANAZOLE) 150MG MEDISPEC</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>24.55</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>CANDID EARDROPS (CLOTRIMAZOLE 1%) 15ML GLENMARK</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="H95" s="10" t="n">
+        <v>18.95</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>VIAL</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>SYR LACTUL (LACTULOSE 670MG/ML) 100ML Y.S.P.</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H97" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>SYR COLIMIX (DICYCLOMINE 5MG/ SIMETHICONE 50MG) 90ML XEPA</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>MDI VENTOLIN EVOHALER (SALBUTAMOL 100MCG) GSK</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H99" s="10" t="n">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>VIAL</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H101" s="10" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>NASAL DROPS ILIADIN 0.01% (OXYMETHAZOLINE) DECONGESTANT (&lt; 12MTHS ) P&amp;G</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>49.68</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H103" s="10" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>EYE/EAR DROPS DEXTRACIN (DEXAMETHASONE &amp; NEOMYCIN) XEPA</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>INJ NON-PREG (MEDROXYPROGESTERONE ACETATE IM 150MG/3ML) VIAL HEALOL PHARMA</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>VIAL</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H105" s="10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>TAB ESCAPELLE (LEVONORGESTREL) 1.5MG 1'S PAHANG PHARMACY</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>TAB SYNFLEX (NAPROXEN SODIUM) 550MG DKSH</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="H107" s="10" t="n">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>VOREN (DICLOFENAC SODIUM 1%W/W) GEL PLUS 20G Y.SP.</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H109" s="10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>PACKET</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>STRIP</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>CHAMPS D-WORMS SUSPENSION (ALBENDAZOLE 200MG/5ML) 10ML DUOPHARMA</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H113" s="10" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>TAB DAFLON (DIOSMIN 900MG, HESPERIDIN 100MG) 1000MG SERVIER</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H114" s="7" t="n">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>FOBAN CREAM (FUSIDIC ACID 2% W/W) 15G HOE</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H115" s="10" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H116" s="7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>ELLGY CORNS &amp; WARTS  (SALICYLIC ACID 17% W/V) 10ML HOE</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="H117" s="10" t="n">
+        <v>29.86</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>FOBANCORT CREAM (FUSIDIC ACID 2% W/W, BETAMETHASONE 0.05% W/W) 15G HOE</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H118" s="7" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="H119" s="10" t="n">
+        <v>13.64</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>INJ LARTIL (PROCHLORPERAZINE MESYLATE)12.5MG/ML 1ML VIAL DUOPHARMA</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>VIAL</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>CERUMOL EAR WAX SOFTNER DROPS 10ML</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H121" s="10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>CIPMAX (CIPROFLOXACIN 0.3%) EYE DROPS 5ML SAMCHUNDANG</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G122" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H122" s="7" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H123" s="10" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="7" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H124" s="7" t="n">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="H125" s="10" t="n">
+        <v>39.04</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>AEVA THYMOL GARGLE 120ML APEX</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H126" s="7" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>DRIMINATE</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H127" s="10" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>KLORAXIN EYE OINTMENT ( CHLORAMPHENICOL 1%) 5G UNIMED</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>TUBE</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H128" s="7" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>INJ TT VACCINE (TETANUS) 0.5ML SM PHARMA</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>0.5ML</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H129" s="10" t="n">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H130" s="7" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>IBUFEN SYRUP (IBUPROFEN 100MG/ 5ML) DYNAPHARM</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>BTL</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H131" s="10" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>INJ PRIORIX (MMR) 0.5ML GSK</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="7" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H132" s="7" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>SYR ENHANCIN (AMOXYCILLIN AND CLAVULANIC ACID 312.5MG/5ML ) 60ML RANBAXY</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H133" s="10" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>INJ PREDON INJECTION 25MG/ML HEALOL PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H134" s="7" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>SYR IXIME ( CEFIXIME 100MG/5ML ) 50ML LUPIN</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>XOIN (N-BUTYL-2-CYANOACRYLATE) TOPICAL SKIN ADHESIVE 0.25ML REEVAX PHARMA</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H136" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>35.71429</v>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>71.43000000000001</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>APPETON A-Z VITAMIN C 30MG PASTILLES 5'S</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G140" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H140" s="7" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
           <t>KETOTOP PLASTER (KETOPROFEN) 30MG 7'S HANDOK</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
         <is>
           <t>PACKET</t>
         </is>
       </c>
-      <c r="E93" s="8" t="n">
+      <c r="E141" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F93" s="8" t="n">
+      <c r="F141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G93" s="10" t="n">
+      <c r="G141" s="10" t="n">
         <v>9.021000000000001</v>
       </c>
-      <c r="H93" s="10" t="n">
+      <c r="H141" s="10" t="n">
         <v>9.02</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H94" s="12" t="n">
-        <v>3291.36</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Total line items: 84</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Generated: 2026-05-28 07:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
+      <c r="H142" s="12" t="n">
+        <v>7124.670000000002</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Total line items: 132</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Generated: 2026-05-28 08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -3331,8 +4867,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A142:G142"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PO_TBD_20260528.xlsx
+++ b/PO_TBD_20260528.xlsx
@@ -4854,7 +4854,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-28 08:00</t>
+          <t>Generated: 2026-05-28 08:43</t>
         </is>
       </c>
     </row>

--- a/PO_TBD_20260528.xlsx
+++ b/PO_TBD_20260528.xlsx
@@ -4854,7 +4854,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-28 08:43</t>
+          <t>Generated: 2026-05-28 08:52</t>
         </is>
       </c>
     </row>

--- a/PO_TBD_20260528.xlsx
+++ b/PO_TBD_20260528.xlsx
@@ -4854,7 +4854,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-28 08:52</t>
+          <t>Generated: 2026-05-28 10:36</t>
         </is>
       </c>
     </row>
